--- a/artfynd/A 23625-2024 artfynd.xlsx
+++ b/artfynd/A 23625-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117911934</v>
+        <v>117911943</v>
       </c>
       <c r="B2" t="n">
-        <v>57287</v>
+        <v>57398</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,17 +708,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Koberget VNV Kall, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>418944</v>
+        <v>418508</v>
       </c>
       <c r="R2" t="n">
-        <v>7045244</v>
+        <v>7045208</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +767,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-06-20</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +793,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117911933</v>
+        <v>117911930</v>
       </c>
       <c r="B3" t="n">
         <v>57287</v>
@@ -822,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>418941</v>
+        <v>418824</v>
       </c>
       <c r="R3" t="n">
-        <v>7045244</v>
+        <v>7045353</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +900,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117911937</v>
+        <v>117911934</v>
       </c>
       <c r="B4" t="n">
         <v>57287</v>
@@ -929,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>418909</v>
+        <v>418944</v>
       </c>
       <c r="R4" t="n">
-        <v>7045110</v>
+        <v>7045244</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +980,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +1007,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117911938</v>
+        <v>117911920</v>
       </c>
       <c r="B5" t="n">
         <v>57287</v>
@@ -1036,10 +1047,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>418769</v>
+        <v>418922</v>
       </c>
       <c r="R5" t="n">
-        <v>7045096</v>
+        <v>7045098</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1087,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1114,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117911935</v>
+        <v>117911936</v>
       </c>
       <c r="B6" t="n">
         <v>57287</v>
@@ -1143,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>418933</v>
+        <v>418968</v>
       </c>
       <c r="R6" t="n">
-        <v>7045229</v>
+        <v>7045185</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1194,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,7 +1221,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117911940</v>
+        <v>117911938</v>
       </c>
       <c r="B7" t="n">
         <v>57287</v>
@@ -1250,10 +1261,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>418583</v>
+        <v>418769</v>
       </c>
       <c r="R7" t="n">
-        <v>7045206</v>
+        <v>7045096</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,7 +1328,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117911930</v>
+        <v>117911940</v>
       </c>
       <c r="B8" t="n">
         <v>57287</v>
@@ -1357,10 +1368,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>418824</v>
+        <v>418583</v>
       </c>
       <c r="R8" t="n">
-        <v>7045353</v>
+        <v>7045206</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1408,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,7 +1435,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117911920</v>
+        <v>117911931</v>
       </c>
       <c r="B9" t="n">
         <v>57287</v>
@@ -1464,10 +1475,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>418922</v>
+        <v>418768</v>
       </c>
       <c r="R9" t="n">
-        <v>7045098</v>
+        <v>7045295</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1531,7 +1542,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117911931</v>
+        <v>117911942</v>
       </c>
       <c r="B10" t="n">
         <v>57287</v>
@@ -1571,10 +1582,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>418768</v>
+        <v>418435</v>
       </c>
       <c r="R10" t="n">
-        <v>7045295</v>
+        <v>7045141</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1622,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,7 +1649,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117911936</v>
+        <v>117911933</v>
       </c>
       <c r="B11" t="n">
         <v>57287</v>
@@ -1678,10 +1689,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>418968</v>
+        <v>418941</v>
       </c>
       <c r="R11" t="n">
-        <v>7045185</v>
+        <v>7045244</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,7 +1729,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,7 +1756,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117911942</v>
+        <v>117911937</v>
       </c>
       <c r="B12" t="n">
         <v>57287</v>
@@ -1785,10 +1796,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>418435</v>
+        <v>418909</v>
       </c>
       <c r="R12" t="n">
-        <v>7045141</v>
+        <v>7045110</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1825,7 +1836,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,10 +1863,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117911943</v>
+        <v>117911935</v>
       </c>
       <c r="B13" t="n">
-        <v>57398</v>
+        <v>57287</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1864,20 +1875,20 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1885,33 +1896,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Koberget VNV Kall, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>418508</v>
+        <v>418933</v>
       </c>
       <c r="R13" t="n">
-        <v>7045208</v>
+        <v>7045229</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1944,6 +1939,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-06-20</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 23625-2024 artfynd.xlsx
+++ b/artfynd/A 23625-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117911943</v>
+        <v>117911930</v>
       </c>
       <c r="B2" t="n">
-        <v>57398</v>
+        <v>57288</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,33 +708,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Koberget VNV Kall, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>418508</v>
+        <v>418824</v>
       </c>
       <c r="R2" t="n">
-        <v>7045208</v>
+        <v>7045353</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -767,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-06-20</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -793,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117911930</v>
+        <v>117911931</v>
       </c>
       <c r="B3" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -833,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>418824</v>
+        <v>418768</v>
       </c>
       <c r="R3" t="n">
-        <v>7045353</v>
+        <v>7045295</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -900,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117911934</v>
+        <v>117911938</v>
       </c>
       <c r="B4" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -940,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>418944</v>
+        <v>418769</v>
       </c>
       <c r="R4" t="n">
-        <v>7045244</v>
+        <v>7045096</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1007,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117911920</v>
+        <v>117911933</v>
       </c>
       <c r="B5" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>418922</v>
+        <v>418941</v>
       </c>
       <c r="R5" t="n">
-        <v>7045098</v>
+        <v>7045244</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1114,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117911936</v>
+        <v>117911940</v>
       </c>
       <c r="B6" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>418968</v>
+        <v>418583</v>
       </c>
       <c r="R6" t="n">
-        <v>7045185</v>
+        <v>7045206</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1221,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117911938</v>
+        <v>117911934</v>
       </c>
       <c r="B7" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>418769</v>
+        <v>418944</v>
       </c>
       <c r="R7" t="n">
-        <v>7045096</v>
+        <v>7045244</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1328,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117911940</v>
+        <v>117911943</v>
       </c>
       <c r="B8" t="n">
-        <v>57287</v>
+        <v>57399</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1340,20 +1329,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1361,17 +1350,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Koberget VNV Kall, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>418583</v>
+        <v>418508</v>
       </c>
       <c r="R8" t="n">
-        <v>7045206</v>
+        <v>7045208</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,11 +1409,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-06-20</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1435,10 +1435,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117911931</v>
+        <v>117911942</v>
       </c>
       <c r="B9" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,10 +1475,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>418768</v>
+        <v>418435</v>
       </c>
       <c r="R9" t="n">
-        <v>7045295</v>
+        <v>7045141</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1542,10 +1542,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117911942</v>
+        <v>117911935</v>
       </c>
       <c r="B10" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1582,10 +1582,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>418435</v>
+        <v>418933</v>
       </c>
       <c r="R10" t="n">
-        <v>7045141</v>
+        <v>7045229</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1622,7 +1622,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1649,10 +1649,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117911933</v>
+        <v>117911937</v>
       </c>
       <c r="B11" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1689,10 +1689,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>418941</v>
+        <v>418909</v>
       </c>
       <c r="R11" t="n">
-        <v>7045244</v>
+        <v>7045110</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1756,10 +1756,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117911937</v>
+        <v>117911936</v>
       </c>
       <c r="B12" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1796,10 +1796,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>418909</v>
+        <v>418968</v>
       </c>
       <c r="R12" t="n">
-        <v>7045110</v>
+        <v>7045185</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1863,10 +1863,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117911935</v>
+        <v>117911920</v>
       </c>
       <c r="B13" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1903,10 +1903,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>418933</v>
+        <v>418922</v>
       </c>
       <c r="R13" t="n">
-        <v>7045229</v>
+        <v>7045098</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 23625-2024 artfynd.xlsx
+++ b/artfynd/A 23625-2024 artfynd.xlsx
@@ -793,7 +793,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117911942</v>
+        <v>117911933</v>
       </c>
       <c r="B3" t="n">
         <v>57290</v>
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>418435</v>
+        <v>418941</v>
       </c>
       <c r="R3" t="n">
-        <v>7045141</v>
+        <v>7045244</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,7 +873,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1007,7 +1007,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117911938</v>
+        <v>117911936</v>
       </c>
       <c r="B5" t="n">
         <v>57290</v>
@@ -1047,10 +1047,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>418769</v>
+        <v>418968</v>
       </c>
       <c r="R5" t="n">
-        <v>7045096</v>
+        <v>7045185</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1114,7 +1114,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117911937</v>
+        <v>117911930</v>
       </c>
       <c r="B6" t="n">
         <v>57290</v>
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>418909</v>
+        <v>418824</v>
       </c>
       <c r="R6" t="n">
-        <v>7045110</v>
+        <v>7045353</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1221,7 +1221,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117911940</v>
+        <v>117911937</v>
       </c>
       <c r="B7" t="n">
         <v>57290</v>
@@ -1261,10 +1261,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>418583</v>
+        <v>418909</v>
       </c>
       <c r="R7" t="n">
-        <v>7045206</v>
+        <v>7045110</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1301,7 +1301,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1328,7 +1328,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117911931</v>
+        <v>117911934</v>
       </c>
       <c r="B8" t="n">
         <v>57290</v>
@@ -1368,10 +1368,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>418768</v>
+        <v>418944</v>
       </c>
       <c r="R8" t="n">
-        <v>7045295</v>
+        <v>7045244</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1435,7 +1435,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117911930</v>
+        <v>117911940</v>
       </c>
       <c r="B9" t="n">
         <v>57290</v>
@@ -1475,10 +1475,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>418824</v>
+        <v>418583</v>
       </c>
       <c r="R9" t="n">
-        <v>7045353</v>
+        <v>7045206</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1542,7 +1542,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117911933</v>
+        <v>117911920</v>
       </c>
       <c r="B10" t="n">
         <v>57290</v>
@@ -1582,10 +1582,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>418941</v>
+        <v>418922</v>
       </c>
       <c r="R10" t="n">
-        <v>7045244</v>
+        <v>7045098</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1649,7 +1649,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117911934</v>
+        <v>117911942</v>
       </c>
       <c r="B11" t="n">
         <v>57290</v>
@@ -1689,10 +1689,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>418944</v>
+        <v>418435</v>
       </c>
       <c r="R11" t="n">
-        <v>7045244</v>
+        <v>7045141</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1756,7 +1756,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117911920</v>
+        <v>117911931</v>
       </c>
       <c r="B12" t="n">
         <v>57290</v>
@@ -1796,10 +1796,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>418922</v>
+        <v>418768</v>
       </c>
       <c r="R12" t="n">
-        <v>7045098</v>
+        <v>7045295</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1863,7 +1863,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117911936</v>
+        <v>117911938</v>
       </c>
       <c r="B13" t="n">
         <v>57290</v>
@@ -1903,10 +1903,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>418968</v>
+        <v>418769</v>
       </c>
       <c r="R13" t="n">
-        <v>7045185</v>
+        <v>7045096</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 23625-2024 artfynd.xlsx
+++ b/artfynd/A 23625-2024 artfynd.xlsx
@@ -793,7 +793,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117911933</v>
+        <v>117911935</v>
       </c>
       <c r="B3" t="n">
         <v>57290</v>
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>418941</v>
+        <v>418933</v>
       </c>
       <c r="R3" t="n">
-        <v>7045244</v>
+        <v>7045229</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -900,7 +900,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117911935</v>
+        <v>117911934</v>
       </c>
       <c r="B4" t="n">
         <v>57290</v>
@@ -940,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>418933</v>
+        <v>418944</v>
       </c>
       <c r="R4" t="n">
-        <v>7045229</v>
+        <v>7045244</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1007,7 +1007,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117911936</v>
+        <v>117911933</v>
       </c>
       <c r="B5" t="n">
         <v>57290</v>
@@ -1047,10 +1047,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>418968</v>
+        <v>418941</v>
       </c>
       <c r="R5" t="n">
-        <v>7045185</v>
+        <v>7045244</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1114,7 +1114,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117911930</v>
+        <v>117911938</v>
       </c>
       <c r="B6" t="n">
         <v>57290</v>
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>418824</v>
+        <v>418769</v>
       </c>
       <c r="R6" t="n">
-        <v>7045353</v>
+        <v>7045096</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1221,7 +1221,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117911937</v>
+        <v>117911930</v>
       </c>
       <c r="B7" t="n">
         <v>57290</v>
@@ -1261,10 +1261,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>418909</v>
+        <v>418824</v>
       </c>
       <c r="R7" t="n">
-        <v>7045110</v>
+        <v>7045353</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1328,7 +1328,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117911934</v>
+        <v>117911937</v>
       </c>
       <c r="B8" t="n">
         <v>57290</v>
@@ -1368,10 +1368,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>418944</v>
+        <v>418909</v>
       </c>
       <c r="R8" t="n">
-        <v>7045244</v>
+        <v>7045110</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1435,7 +1435,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117911940</v>
+        <v>117911936</v>
       </c>
       <c r="B9" t="n">
         <v>57290</v>
@@ -1475,10 +1475,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>418583</v>
+        <v>418968</v>
       </c>
       <c r="R9" t="n">
-        <v>7045206</v>
+        <v>7045185</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1542,7 +1542,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117911920</v>
+        <v>117911940</v>
       </c>
       <c r="B10" t="n">
         <v>57290</v>
@@ -1582,10 +1582,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>418922</v>
+        <v>418583</v>
       </c>
       <c r="R10" t="n">
-        <v>7045098</v>
+        <v>7045206</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1622,7 +1622,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1649,7 +1649,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117911942</v>
+        <v>117911931</v>
       </c>
       <c r="B11" t="n">
         <v>57290</v>
@@ -1689,10 +1689,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>418435</v>
+        <v>418768</v>
       </c>
       <c r="R11" t="n">
-        <v>7045141</v>
+        <v>7045295</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1729,7 +1729,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1756,7 +1756,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117911931</v>
+        <v>117911942</v>
       </c>
       <c r="B12" t="n">
         <v>57290</v>
@@ -1796,10 +1796,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>418768</v>
+        <v>418435</v>
       </c>
       <c r="R12" t="n">
-        <v>7045295</v>
+        <v>7045141</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1863,7 +1863,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117911938</v>
+        <v>117911920</v>
       </c>
       <c r="B13" t="n">
         <v>57290</v>
@@ -1903,10 +1903,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>418769</v>
+        <v>418922</v>
       </c>
       <c r="R13" t="n">
-        <v>7045096</v>
+        <v>7045098</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1943,7 +1943,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 23625-2024 artfynd.xlsx
+++ b/artfynd/A 23625-2024 artfynd.xlsx
@@ -793,7 +793,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117911935</v>
+        <v>117911942</v>
       </c>
       <c r="B3" t="n">
         <v>57290</v>
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>418933</v>
+        <v>418435</v>
       </c>
       <c r="R3" t="n">
-        <v>7045229</v>
+        <v>7045141</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,7 +873,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1007,7 +1007,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117911933</v>
+        <v>117911936</v>
       </c>
       <c r="B5" t="n">
         <v>57290</v>
@@ -1047,10 +1047,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>418941</v>
+        <v>418968</v>
       </c>
       <c r="R5" t="n">
-        <v>7045244</v>
+        <v>7045185</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1114,7 +1114,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117911938</v>
+        <v>117911920</v>
       </c>
       <c r="B6" t="n">
         <v>57290</v>
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>418769</v>
+        <v>418922</v>
       </c>
       <c r="R6" t="n">
-        <v>7045096</v>
+        <v>7045098</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1221,7 +1221,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117911930</v>
+        <v>117911938</v>
       </c>
       <c r="B7" t="n">
         <v>57290</v>
@@ -1261,10 +1261,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>418824</v>
+        <v>418769</v>
       </c>
       <c r="R7" t="n">
-        <v>7045353</v>
+        <v>7045096</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1301,7 +1301,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1328,7 +1328,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117911937</v>
+        <v>117911940</v>
       </c>
       <c r="B8" t="n">
         <v>57290</v>
@@ -1368,10 +1368,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>418909</v>
+        <v>418583</v>
       </c>
       <c r="R8" t="n">
-        <v>7045110</v>
+        <v>7045206</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1435,7 +1435,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117911936</v>
+        <v>117911937</v>
       </c>
       <c r="B9" t="n">
         <v>57290</v>
@@ -1475,10 +1475,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>418968</v>
+        <v>418909</v>
       </c>
       <c r="R9" t="n">
-        <v>7045185</v>
+        <v>7045110</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1542,7 +1542,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117911940</v>
+        <v>117911930</v>
       </c>
       <c r="B10" t="n">
         <v>57290</v>
@@ -1582,10 +1582,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>418583</v>
+        <v>418824</v>
       </c>
       <c r="R10" t="n">
-        <v>7045206</v>
+        <v>7045353</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1622,7 +1622,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1756,7 +1756,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117911942</v>
+        <v>117911933</v>
       </c>
       <c r="B12" t="n">
         <v>57290</v>
@@ -1796,10 +1796,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>418435</v>
+        <v>418941</v>
       </c>
       <c r="R12" t="n">
-        <v>7045141</v>
+        <v>7045244</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1863,7 +1863,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117911920</v>
+        <v>117911935</v>
       </c>
       <c r="B13" t="n">
         <v>57290</v>
@@ -1903,10 +1903,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>418922</v>
+        <v>418933</v>
       </c>
       <c r="R13" t="n">
-        <v>7045098</v>
+        <v>7045229</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 23625-2024 artfynd.xlsx
+++ b/artfynd/A 23625-2024 artfynd.xlsx
@@ -793,7 +793,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117911942</v>
+        <v>117911936</v>
       </c>
       <c r="B3" t="n">
         <v>57290</v>
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>418435</v>
+        <v>418968</v>
       </c>
       <c r="R3" t="n">
-        <v>7045141</v>
+        <v>7045185</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -900,7 +900,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117911934</v>
+        <v>117911937</v>
       </c>
       <c r="B4" t="n">
         <v>57290</v>
@@ -940,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>418944</v>
+        <v>418909</v>
       </c>
       <c r="R4" t="n">
-        <v>7045244</v>
+        <v>7045110</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1007,7 +1007,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117911936</v>
+        <v>117911938</v>
       </c>
       <c r="B5" t="n">
         <v>57290</v>
@@ -1047,10 +1047,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>418968</v>
+        <v>418769</v>
       </c>
       <c r="R5" t="n">
-        <v>7045185</v>
+        <v>7045096</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1114,7 +1114,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117911920</v>
+        <v>117911930</v>
       </c>
       <c r="B6" t="n">
         <v>57290</v>
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>418922</v>
+        <v>418824</v>
       </c>
       <c r="R6" t="n">
-        <v>7045098</v>
+        <v>7045353</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1221,7 +1221,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117911938</v>
+        <v>117911934</v>
       </c>
       <c r="B7" t="n">
         <v>57290</v>
@@ -1261,10 +1261,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>418769</v>
+        <v>418944</v>
       </c>
       <c r="R7" t="n">
-        <v>7045096</v>
+        <v>7045244</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1435,7 +1435,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117911937</v>
+        <v>117911933</v>
       </c>
       <c r="B9" t="n">
         <v>57290</v>
@@ -1475,10 +1475,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>418909</v>
+        <v>418941</v>
       </c>
       <c r="R9" t="n">
-        <v>7045110</v>
+        <v>7045244</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1542,7 +1542,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117911930</v>
+        <v>117911935</v>
       </c>
       <c r="B10" t="n">
         <v>57290</v>
@@ -1582,10 +1582,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>418824</v>
+        <v>418933</v>
       </c>
       <c r="R10" t="n">
-        <v>7045353</v>
+        <v>7045229</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1649,7 +1649,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117911931</v>
+        <v>117911942</v>
       </c>
       <c r="B11" t="n">
         <v>57290</v>
@@ -1689,10 +1689,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>418768</v>
+        <v>418435</v>
       </c>
       <c r="R11" t="n">
-        <v>7045295</v>
+        <v>7045141</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1729,7 +1729,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1756,7 +1756,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117911933</v>
+        <v>117911920</v>
       </c>
       <c r="B12" t="n">
         <v>57290</v>
@@ -1796,10 +1796,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>418941</v>
+        <v>418922</v>
       </c>
       <c r="R12" t="n">
-        <v>7045244</v>
+        <v>7045098</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1863,7 +1863,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117911935</v>
+        <v>117911931</v>
       </c>
       <c r="B13" t="n">
         <v>57290</v>
@@ -1903,10 +1903,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>418933</v>
+        <v>418768</v>
       </c>
       <c r="R13" t="n">
-        <v>7045229</v>
+        <v>7045295</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
